--- a/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/california ground squirrel.xlsx
+++ b/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/california ground squirrel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachael\OneDrive\Documents\PS30094 Dissertation\Brain area data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C910CEF-9058-40FD-B0B7-57242B931A15}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{6C910CEF-9058-40FD-B0B7-57242B931A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995F5C65-6B39-6349-B32B-79EBC0D38D2F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DF509882-127E-4C47-8D16-EB2ED3AC3199}"/>
+    <workbookView xWindow="82000" yWindow="-2600" windowWidth="18660" windowHeight="10420" xr2:uid="{DF509882-127E-4C47-8D16-EB2ED3AC3199}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -243,9 +243,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -283,7 +283,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -389,7 +389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -531,7 +531,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -540,9 +540,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2574D31D-8BF4-4549-83B5-7463F04944B9}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -583,7 +583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -631,7 +631,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -683,7 +683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J5" t="s">
         <v>28</v>
       </c>
@@ -743,7 +743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J6" t="s">
         <v>29</v>
       </c>
@@ -758,7 +758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J7" t="s">
         <v>30</v>
       </c>
@@ -773,7 +773,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
         <v>31</v>
       </c>
@@ -791,7 +791,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
@@ -827,7 +827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J10" t="s">
         <v>33</v>
       </c>
@@ -842,7 +842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5</v>
       </c>
@@ -878,7 +878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>6</v>
       </c>
@@ -914,7 +914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J13" t="s">
         <v>35</v>
       </c>
@@ -929,7 +929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J14">
         <v>1</v>
       </c>
@@ -944,7 +944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>7</v>
       </c>
@@ -980,7 +980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="J16" t="s">
         <v>37</v>
       </c>
@@ -995,7 +995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="10:14" x14ac:dyDescent="0.2">
       <c r="J17" t="s">
         <v>38</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="10:14" x14ac:dyDescent="0.2">
       <c r="J18" t="s">
         <v>39</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="10:14" x14ac:dyDescent="0.2">
       <c r="J19" t="s">
         <v>40</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="10:14" x14ac:dyDescent="0.2">
       <c r="J20" t="s">
         <v>41</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="10:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="10:14" x14ac:dyDescent="0.2">
       <c r="J21" t="s">
         <v>43</v>
       </c>
@@ -1328,9 +1328,28 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A89D5D-A5A3-48C9-8FDC-9C93C86B232A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11A89D5D-A5A3-48C9-8FDC-9C93C86B232A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AE6204C-E5D0-49FE-BA66-6C912A941090}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AE6204C-E5D0-49FE-BA66-6C912A941090}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>